--- a/artfynd/A 50770-2022 artfynd.xlsx
+++ b/artfynd/A 50770-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,6 +798,123 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129465232</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Boramossen, Boramossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>470950</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6539457</v>
+      </c>
+      <c r="S3" t="n">
+        <v>20</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska spår på tall vid höjd</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50770-2022 artfynd.xlsx
+++ b/artfynd/A 50770-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129465387</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>129465232</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50770-2022 artfynd.xlsx
+++ b/artfynd/A 50770-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129465387</v>
       </c>
       <c r="B2" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>129465232</v>
       </c>
       <c r="B3" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50770-2022 artfynd.xlsx
+++ b/artfynd/A 50770-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129465387</v>
       </c>
       <c r="B2" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>129465232</v>
       </c>
       <c r="B3" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50770-2022 artfynd.xlsx
+++ b/artfynd/A 50770-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -916,6 +916,474 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130017146</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Boramossen, Boramossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>470988</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6539528</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska födohack på granlåga.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130017134</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Boramossen, Boramossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>470964</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6539492</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska spår, ringhack, högt upp på tall</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130017230</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Boramossen, Boramossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>470895</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6539657</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack med savflöde och äldre ringhack på tall märkt med rött märkband.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130017088</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Boramossen, Boramossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>470928</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6539451</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre födohack på granlåga</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50770-2022 artfynd.xlsx
+++ b/artfynd/A 50770-2022 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>130017146</v>
       </c>
       <c r="B4" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>130017134</v>
       </c>
       <c r="B5" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>130017230</v>
       </c>
       <c r="B6" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>130017088</v>
       </c>
       <c r="B7" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 50770-2022 artfynd.xlsx
+++ b/artfynd/A 50770-2022 artfynd.xlsx
@@ -1503,27 +1503,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130501880</v>
+        <v>130502019</v>
       </c>
       <c r="B9" t="n">
-        <v>57667</v>
+        <v>57823</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102621</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1534,7 +1534,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1578,22 +1578,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1620,27 +1620,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130502019</v>
+        <v>130501880</v>
       </c>
       <c r="B10" t="n">
-        <v>57823</v>
+        <v>57667</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>102621</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1695,22 +1695,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 50770-2022 artfynd.xlsx
+++ b/artfynd/A 50770-2022 artfynd.xlsx
@@ -1389,7 +1389,7 @@
         <v>130325451</v>
       </c>
       <c r="B8" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>130502019</v>
       </c>
       <c r="B9" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>130501880</v>
       </c>
       <c r="B10" t="n">
-        <v>57667</v>
+        <v>57693</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 50770-2022 artfynd.xlsx
+++ b/artfynd/A 50770-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1618,123 +1618,6 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>130501880</v>
-      </c>
-      <c r="B10" t="n">
-        <v>57693</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>102621</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Sparvuggla</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Glaucidium passerinum</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Boramossen, Boramossen, Vg</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>470944</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6539508</v>
-      </c>
-      <c r="S10" t="n">
-        <v>100</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Laxå</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Finnerödja</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>David Tverling</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>David Tverling</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50770-2022 artfynd.xlsx
+++ b/artfynd/A 50770-2022 artfynd.xlsx
@@ -1389,7 +1389,7 @@
         <v>130325451</v>
       </c>
       <c r="B8" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>130502019</v>
       </c>
       <c r="B9" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 50770-2022 artfynd.xlsx
+++ b/artfynd/A 50770-2022 artfynd.xlsx
@@ -1389,7 +1389,7 @@
         <v>130325451</v>
       </c>
       <c r="B8" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>130502019</v>
       </c>
       <c r="B9" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 50770-2022 artfynd.xlsx
+++ b/artfynd/A 50770-2022 artfynd.xlsx
@@ -1389,7 +1389,7 @@
         <v>130325451</v>
       </c>
       <c r="B8" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>130502019</v>
       </c>
       <c r="B9" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 50770-2022 artfynd.xlsx
+++ b/artfynd/A 50770-2022 artfynd.xlsx
@@ -1389,7 +1389,7 @@
         <v>130325451</v>
       </c>
       <c r="B8" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>130502019</v>
       </c>
       <c r="B9" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 50770-2022 artfynd.xlsx
+++ b/artfynd/A 50770-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129465387</v>
       </c>
       <c r="B2" t="n">
-        <v>57736</v>
+        <v>57864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50770-2022 artfynd.xlsx
+++ b/artfynd/A 50770-2022 artfynd.xlsx
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129465387</v>
+        <v>130017088</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -703,19 +703,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>470786</v>
+        <v>470928</v>
       </c>
       <c r="R2" t="n">
-        <v>6539519</v>
+        <v>6539451</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -754,27 +745,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Satt långt ner på gran och födosökte ca 10 m ifrån mig. Inne i avverkningsanmälan. Bild på var den födosökte och hack efter den.</t>
+          <t>Äldre födohack på granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,27 +792,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129465232</v>
+        <v>130017146</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -841,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>470950</v>
+        <v>470988</v>
       </c>
       <c r="R3" t="n">
-        <v>6539457</v>
+        <v>6539528</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -871,27 +862,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Färska spår på tall vid höjd</t>
+          <t>Färska födohack på granlåga.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,26 +897,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130017146</v>
+        <v>130325451</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -949,7 +940,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -958,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>470988</v>
+        <v>470947</v>
       </c>
       <c r="R4" t="n">
-        <v>6539528</v>
+        <v>6539526</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -988,27 +979,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska födohack på granlåga.</t>
+          <t>Äldre födohack vid basen av granlåga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,27 +1026,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130017134</v>
+        <v>130502019</v>
       </c>
       <c r="B5" t="n">
-        <v>57826</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1066,7 +1057,12 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1075,13 +1071,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>470964</v>
+        <v>470944</v>
       </c>
       <c r="R5" t="n">
-        <v>6539492</v>
+        <v>6539508</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,27 +1101,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska spår, ringhack, högt upp på tall</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130017230</v>
+        <v>129465232</v>
       </c>
       <c r="B6" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>470895</v>
+        <v>470950</v>
       </c>
       <c r="R6" t="n">
-        <v>6539657</v>
+        <v>6539457</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1222,27 +1213,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färska ringhack med savflöde och äldre ringhack på tall märkt med rött märkband.</t>
+          <t>Färska spår på tall vid höjd</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,22 +1248,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130017088</v>
+        <v>129465387</v>
       </c>
       <c r="B7" t="n">
-        <v>57823</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,16 +1271,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1297,10 +1288,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1309,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>470928</v>
+        <v>470786</v>
       </c>
       <c r="R7" t="n">
-        <v>6539451</v>
+        <v>6539519</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1339,27 +1339,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Äldre födohack på granlåga</t>
+          <t>Satt långt ner på gran och födosökte ca 10 m ifrån mig. Inne i avverkningsanmälan. Bild på var den födosökte och hack efter den.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130325451</v>
+        <v>130017134</v>
       </c>
       <c r="B8" t="n">
-        <v>57861</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,16 +1397,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1417,7 +1417,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1426,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>470947</v>
+        <v>470964</v>
       </c>
       <c r="R8" t="n">
-        <v>6539526</v>
+        <v>6539492</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1456,27 +1456,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Äldre födohack vid basen av granlåga.</t>
+          <t>Färska spår, ringhack, högt upp på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,22 +1491,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130502019</v>
+        <v>130017230</v>
       </c>
       <c r="B9" t="n">
-        <v>57875</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,16 +1514,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1534,12 +1534,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1548,13 +1543,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>470944</v>
+        <v>470895</v>
       </c>
       <c r="R9" t="n">
-        <v>6539508</v>
+        <v>6539657</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1578,22 +1573,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack med savflöde och äldre ringhack på tall märkt med rött märkband.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,12 +1608,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 50770-2022 artfynd.xlsx
+++ b/artfynd/A 50770-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130017088</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130017146</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1023,6 +1038,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130325451</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1140,6 +1160,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130502019</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1257,6 +1282,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129465232</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1383,6 +1413,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129465387</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1500,6 +1535,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130017134</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1617,8 +1657,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130017230</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>